--- a/APP/docs/UI/APP_UI_第三版本_修正版.xlsx
+++ b/APP/docs/UI/APP_UI_第三版本_修正版.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="3"/>
+    <workbookView windowHeight="17655" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="说明页" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="215">
   <si>
     <t>项目说明
 1. 一个单元格代表 8*8 像素格, 整个屏幕是 W:128 * H:64 像素 OLED 屏。
@@ -436,34 +436,49 @@
     <t>Up/Down SEL    Left/Right ADJ    Left Long BACK</t>
   </si>
   <si>
-    <t>页面说明: 热管理模块详情页, 使用完整 128*56 内容区。Up/Down 选择 HEAT/FAN/TARGET 字段; Left/Right 即时切换加热或散热模式; Enter Short 执行/确认当前项; Left Long 返回 HOME总览; Enter Long 保留系统开关机。</t>
-  </si>
-  <si>
-    <t>HEAT  (左对齐, 白底黑字)</t>
+    <t>页面说明: 热管理模块详情页, 使用完整 128*56 内容区。Up/Down 选择 WATER/HEAT/HeatTargetTemp/FAN/FanTempStart/FanTempFull 字段; Enter Short 执行/确认当前项; Left Long 返回 HOME总览; Enter Long 保留系统开关机。
+HeatTargetTemp,FanTempStart,FanTempFull通过Left/Right调节大小.
+HEAT,FAN通过Left/Right切换开关.
+最后一行FanTempFull是超出页面显示范围的,所以要做成可以通过上下按键来实现画面上下移动</t>
+  </si>
+  <si>
+    <t>HM  (左对齐, 白底黑字)</t>
   </si>
   <si>
     <t>WATER</t>
   </si>
   <si>
-    <t>--.-C</t>
+    <t>sMaxTemp/sMinTemp</t>
   </si>
   <si>
     <t>HEAT</t>
   </si>
   <si>
-    <t>OFF / KEEP / HIGH / MAN</t>
+    <t>bHeatEnable/Heat_PWM</t>
+  </si>
+  <si>
+    <t>HeatTargetTemp</t>
+  </si>
+  <si>
+    <t>sHeatTargetTemp</t>
   </si>
   <si>
     <t>FAN</t>
   </si>
   <si>
-    <t>OFF / LOW / MID / HIGH / FULL</t>
-  </si>
-  <si>
-    <t>TARGET</t>
-  </si>
-  <si>
-    <t>25C</t>
+    <t>bFanEnable/FAN_PWM</t>
+  </si>
+  <si>
+    <t>FanTempStart</t>
+  </si>
+  <si>
+    <t>sFanTempStart</t>
+  </si>
+  <si>
+    <t>FanTempFull</t>
+  </si>
+  <si>
+    <t>sFanTempFull</t>
   </si>
   <si>
     <t>页面说明: 水泵模块详情页, 使用完整 128*56 内容区。Left/Right 即时切换 MODE; Enter Short 执行/确认当前模式; Left Long 返回 HOME总览; Enter Long 保留系统开关机。若后续增加更多字段, Up/Down 可用于选择字段。</t>
@@ -552,6 +567,9 @@
   </si>
   <si>
     <t>WT1</t>
+  </si>
+  <si>
+    <t>--.-C</t>
   </si>
   <si>
     <t>WT2</t>
@@ -1069,7 +1087,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="40">
+  <borders count="41">
     <border>
       <left/>
       <right/>
@@ -1182,6 +1200,17 @@
         <color rgb="FFA6A6A6"/>
       </right>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFA6A6A6"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFA6A6A6"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -1540,7 +1569,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="32">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="33">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
@@ -1552,34 +1581,34 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="33">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="34">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="33">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="34">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="35">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="35">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="36">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="36">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="37">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="35">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="36">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="37">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="38">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="38">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="39">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="39">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="40">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
@@ -1664,7 +1693,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1696,42 +1725,60 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2141,40 +2188,40 @@
       <c r="N3" s="7"/>
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:14">
-      <c r="A4" s="38" t="s">
+      <c r="A4" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="38" t="s">
+      <c r="C4" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="38" t="s">
+      <c r="D4" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="38" t="s">
+      <c r="E4" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="38" t="s">
+      <c r="F4" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="38" t="s">
+      <c r="G4" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="38" t="s">
+      <c r="H4" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="38" t="s">
+      <c r="I4" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="J4" s="38" t="s">
+      <c r="J4" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="K4" s="38" t="s">
+      <c r="K4" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="L4" s="38" t="s">
+      <c r="L4" s="44" t="s">
         <v>12</v>
       </c>
       <c r="M4" s="7"/>
@@ -2221,7 +2268,7 @@
       <c r="N5" s="7"/>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:14">
-      <c r="A6" s="39"/>
+      <c r="A6" s="45"/>
       <c r="B6" s="7" t="s">
         <v>20</v>
       </c>
@@ -2259,7 +2306,7 @@
       <c r="N6" s="7"/>
     </row>
     <row r="7" ht="58" customHeight="1" spans="1:14">
-      <c r="A7" s="39"/>
+      <c r="A7" s="45"/>
       <c r="B7" s="7" t="s">
         <v>24</v>
       </c>
@@ -2297,7 +2344,7 @@
       <c r="N7" s="7"/>
     </row>
     <row r="8" ht="58" customHeight="1" spans="1:14">
-      <c r="A8" s="39"/>
+      <c r="A8" s="45"/>
       <c r="B8" s="7" t="s">
         <v>33</v>
       </c>
@@ -2335,7 +2382,7 @@
       <c r="N8" s="7"/>
     </row>
     <row r="9" ht="58" customHeight="1" spans="1:14">
-      <c r="A9" s="39"/>
+      <c r="A9" s="45"/>
       <c r="B9" s="7" t="s">
         <v>43</v>
       </c>
@@ -2373,7 +2420,7 @@
       <c r="N9" s="7"/>
     </row>
     <row r="10" ht="58" customHeight="1" spans="1:14">
-      <c r="A10" s="39"/>
+      <c r="A10" s="45"/>
       <c r="B10" s="7" t="s">
         <v>47</v>
       </c>
@@ -2411,7 +2458,7 @@
       <c r="N10" s="7"/>
     </row>
     <row r="11" ht="58" customHeight="1" spans="1:14">
-      <c r="A11" s="39"/>
+      <c r="A11" s="45"/>
       <c r="B11" s="7" t="s">
         <v>56</v>
       </c>
@@ -2449,7 +2496,7 @@
       <c r="N11" s="7"/>
     </row>
     <row r="12" ht="58" customHeight="1" spans="1:14">
-      <c r="A12" s="39"/>
+      <c r="A12" s="45"/>
       <c r="B12" s="7" t="s">
         <v>59</v>
       </c>
@@ -2487,7 +2534,7 @@
       <c r="N12" s="7"/>
     </row>
     <row r="13" ht="58" customHeight="1" spans="1:14">
-      <c r="A13" s="39"/>
+      <c r="A13" s="45"/>
       <c r="B13" s="7" t="s">
         <v>67</v>
       </c>
@@ -2525,7 +2572,7 @@
       <c r="N13" s="7"/>
     </row>
     <row r="14" ht="38" customHeight="1" spans="1:14">
-      <c r="A14" s="39"/>
+      <c r="A14" s="45"/>
       <c r="B14" s="7" t="s">
         <v>73</v>
       </c>
@@ -2563,7 +2610,7 @@
       <c r="N14" s="7"/>
     </row>
     <row r="15" ht="38" customHeight="1" spans="1:14">
-      <c r="A15" s="39"/>
+      <c r="A15" s="45"/>
       <c r="B15" s="7" t="s">
         <v>77</v>
       </c>
@@ -2601,7 +2648,7 @@
       <c r="N15" s="7"/>
     </row>
     <row r="16" ht="38" customHeight="1" spans="1:14">
-      <c r="A16" s="40"/>
+      <c r="A16" s="46"/>
       <c r="B16" s="7" t="s">
         <v>83</v>
       </c>
@@ -2790,7 +2837,7 @@
   <sheetData>
     <row r="1" ht="95" customHeight="1" spans="1:16">
       <c r="A1" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -2810,7 +2857,7 @@
     </row>
     <row r="2" ht="56.65" customHeight="1" spans="1:16">
       <c r="A2" s="5" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -2830,7 +2877,7 @@
     </row>
     <row r="3" ht="56.65" customHeight="1" spans="1:16">
       <c r="A3" s="6" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -2838,7 +2885,7 @@
       <c r="E3" s="3"/>
       <c r="F3" s="4"/>
       <c r="G3" s="6" t="s">
-        <v>132</v>
+        <v>172</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
@@ -2852,7 +2899,7 @@
     </row>
     <row r="4" ht="56.65" customHeight="1" spans="1:16">
       <c r="A4" s="6" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -2860,7 +2907,7 @@
       <c r="E4" s="3"/>
       <c r="F4" s="4"/>
       <c r="G4" s="6" t="s">
-        <v>132</v>
+        <v>172</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
@@ -2874,7 +2921,7 @@
     </row>
     <row r="5" ht="56.65" customHeight="1" spans="1:16">
       <c r="A5" s="6" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -2882,7 +2929,7 @@
       <c r="E5" s="3"/>
       <c r="F5" s="4"/>
       <c r="G5" s="6" t="s">
-        <v>132</v>
+        <v>172</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
@@ -2896,7 +2943,7 @@
     </row>
     <row r="6" ht="56.65" customHeight="1" spans="1:16">
       <c r="A6" s="6" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -2904,7 +2951,7 @@
       <c r="E6" s="3"/>
       <c r="F6" s="4"/>
       <c r="G6" s="6" t="s">
-        <v>132</v>
+        <v>172</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
@@ -2918,7 +2965,7 @@
     </row>
     <row r="7" ht="56.65" customHeight="1" spans="1:16">
       <c r="A7" s="6" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -2926,7 +2973,7 @@
       <c r="E7" s="3"/>
       <c r="F7" s="4"/>
       <c r="G7" s="6" t="s">
-        <v>132</v>
+        <v>172</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
@@ -2940,7 +2987,7 @@
     </row>
     <row r="8" ht="56.65" customHeight="1" spans="1:16">
       <c r="A8" s="6" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -2960,7 +3007,7 @@
     </row>
     <row r="9" ht="56.65" customHeight="1" spans="1:16">
       <c r="A9" s="6" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -2998,7 +3045,7 @@
     </row>
     <row r="11" ht="56.65" customHeight="1" spans="1:16">
       <c r="A11" s="5" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -3018,7 +3065,7 @@
     </row>
     <row r="12" ht="56.65" customHeight="1" spans="1:16">
       <c r="A12" s="6" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -3026,7 +3073,7 @@
       <c r="E12" s="3"/>
       <c r="F12" s="4"/>
       <c r="G12" s="6" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
@@ -3040,7 +3087,7 @@
     </row>
     <row r="13" ht="56.65" customHeight="1" spans="1:16">
       <c r="A13" s="6" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -3048,7 +3095,7 @@
       <c r="E13" s="3"/>
       <c r="F13" s="4"/>
       <c r="G13" s="6" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
@@ -3062,7 +3109,7 @@
     </row>
     <row r="14" ht="56.65" customHeight="1" spans="1:16">
       <c r="A14" s="6" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -3070,7 +3117,7 @@
       <c r="E14" s="3"/>
       <c r="F14" s="4"/>
       <c r="G14" s="6" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
@@ -3084,7 +3131,7 @@
     </row>
     <row r="15" ht="56.65" customHeight="1" spans="1:16">
       <c r="A15" s="6" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -3092,7 +3139,7 @@
       <c r="E15" s="3"/>
       <c r="F15" s="4"/>
       <c r="G15" s="6" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
@@ -3106,7 +3153,7 @@
     </row>
     <row r="16" ht="56.65" customHeight="1" spans="1:16">
       <c r="A16" s="6" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -3114,7 +3161,7 @@
       <c r="E16" s="3"/>
       <c r="F16" s="4"/>
       <c r="G16" s="6" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
@@ -3128,7 +3175,7 @@
     </row>
     <row r="17" ht="56.65" customHeight="1" spans="1:16">
       <c r="A17" s="6" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -3148,7 +3195,7 @@
     </row>
     <row r="18" ht="56.65" customHeight="1" spans="1:16">
       <c r="A18" s="6" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -3186,7 +3233,7 @@
     </row>
     <row r="20" ht="56.65" customHeight="1" spans="1:16">
       <c r="A20" s="5" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -3206,7 +3253,7 @@
     </row>
     <row r="21" ht="56.65" customHeight="1" spans="1:16">
       <c r="A21" s="6" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -3214,7 +3261,7 @@
       <c r="E21" s="3"/>
       <c r="F21" s="4"/>
       <c r="G21" s="6" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
@@ -3228,7 +3275,7 @@
     </row>
     <row r="22" ht="56.65" customHeight="1" spans="1:16">
       <c r="A22" s="6" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -3258,7 +3305,7 @@
       <c r="E23" s="3"/>
       <c r="F23" s="4"/>
       <c r="G23" s="6" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
@@ -3280,7 +3327,7 @@
       <c r="E24" s="3"/>
       <c r="F24" s="4"/>
       <c r="G24" s="6" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
@@ -3294,7 +3341,7 @@
     </row>
     <row r="25" ht="56.65" customHeight="1" spans="1:16">
       <c r="A25" s="6" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -3302,7 +3349,7 @@
       <c r="E25" s="3"/>
       <c r="F25" s="4"/>
       <c r="G25" s="6" t="s">
-        <v>132</v>
+        <v>172</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
@@ -3316,7 +3363,7 @@
     </row>
     <row r="26" ht="56.65" customHeight="1" spans="1:16">
       <c r="A26" s="6" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -3336,7 +3383,7 @@
     </row>
     <row r="27" ht="56.65" customHeight="1" spans="1:16">
       <c r="A27" s="6" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -3470,7 +3517,7 @@
   <sheetData>
     <row r="1" ht="95" customHeight="1" spans="1:16">
       <c r="A1" s="2" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -3490,7 +3537,7 @@
     </row>
     <row r="2" ht="56.65" customHeight="1" spans="1:16">
       <c r="A2" s="5" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -3510,7 +3557,7 @@
     </row>
     <row r="3" ht="56.65" customHeight="1" spans="1:16">
       <c r="A3" s="7" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -3564,7 +3611,7 @@
     </row>
     <row r="9" ht="56.65" customHeight="1" spans="1:16">
       <c r="A9" s="7" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -3659,7 +3706,7 @@
   <sheetData>
     <row r="1" ht="95" customHeight="1" spans="1:16">
       <c r="A1" s="2" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -3679,7 +3726,7 @@
     </row>
     <row r="2" ht="56.65" customHeight="1" spans="1:16">
       <c r="A2" s="5" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -3699,7 +3746,7 @@
     </row>
     <row r="3" ht="56.65" customHeight="1" spans="1:16">
       <c r="A3" s="7" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -3753,7 +3800,7 @@
     </row>
     <row r="9" ht="56.65" customHeight="1" spans="1:16">
       <c r="A9" s="7" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -3851,7 +3898,7 @@
   <sheetData>
     <row r="1" ht="95" customHeight="1" spans="1:16">
       <c r="A1" s="2" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -3871,7 +3918,7 @@
     </row>
     <row r="2" ht="56.65" customHeight="1" spans="1:16">
       <c r="A2" s="5" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -3891,7 +3938,7 @@
     </row>
     <row r="3" ht="56.65" customHeight="1" spans="1:16">
       <c r="A3" s="6" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -3899,7 +3946,7 @@
       <c r="E3" s="3"/>
       <c r="F3" s="4"/>
       <c r="G3" s="6" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
@@ -3913,7 +3960,7 @@
     </row>
     <row r="4" ht="56.65" customHeight="1" spans="1:16">
       <c r="A4" s="6" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -3921,7 +3968,7 @@
       <c r="E4" s="3"/>
       <c r="F4" s="4"/>
       <c r="G4" s="6" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
@@ -3935,7 +3982,7 @@
     </row>
     <row r="5" ht="56.65" customHeight="1" spans="1:16">
       <c r="A5" s="6" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -3943,7 +3990,7 @@
       <c r="E5" s="3"/>
       <c r="F5" s="4"/>
       <c r="G5" s="6" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
@@ -3957,7 +4004,7 @@
     </row>
     <row r="6" ht="56.65" customHeight="1" spans="1:16">
       <c r="A6" s="6" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -3965,7 +4012,7 @@
       <c r="E6" s="3"/>
       <c r="F6" s="4"/>
       <c r="G6" s="6" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
@@ -3979,7 +4026,7 @@
     </row>
     <row r="7" ht="56.65" customHeight="1" spans="1:16">
       <c r="A7" s="7" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -4017,7 +4064,7 @@
     </row>
     <row r="9" ht="56.65" customHeight="1" spans="1:16">
       <c r="A9" s="6" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -4121,122 +4168,122 @@
   </cols>
   <sheetData>
     <row r="1" ht="56.65" customHeight="1" spans="1:16">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="32" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="28"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="34"/>
     </row>
     <row r="2" ht="56.65" customHeight="1" spans="1:16">
-      <c r="A2" s="29"/>
-      <c r="E2" s="17" t="s">
+      <c r="A2" s="35"/>
+      <c r="E2" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="31"/>
-      <c r="P2" s="32"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="36"/>
+      <c r="L2" s="37"/>
+      <c r="P2" s="38"/>
     </row>
     <row r="3" ht="56.65" customHeight="1" spans="1:16">
-      <c r="A3" s="29"/>
-      <c r="E3" s="33"/>
-      <c r="L3" s="34"/>
-      <c r="P3" s="32"/>
+      <c r="A3" s="35"/>
+      <c r="E3" s="39"/>
+      <c r="L3" s="40"/>
+      <c r="P3" s="38"/>
     </row>
     <row r="4" ht="56.65" customHeight="1" spans="1:16">
-      <c r="A4" s="29"/>
-      <c r="E4" s="33"/>
-      <c r="L4" s="34"/>
-      <c r="P4" s="32"/>
+      <c r="A4" s="35"/>
+      <c r="E4" s="39"/>
+      <c r="L4" s="40"/>
+      <c r="P4" s="38"/>
     </row>
     <row r="5" ht="56.65" customHeight="1" spans="1:16">
-      <c r="A5" s="29"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="36"/>
-      <c r="K5" s="36"/>
-      <c r="L5" s="37"/>
-      <c r="P5" s="32"/>
+      <c r="A5" s="35"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="42"/>
+      <c r="K5" s="42"/>
+      <c r="L5" s="43"/>
+      <c r="P5" s="38"/>
     </row>
     <row r="6" ht="56.65" customHeight="1" spans="1:16">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="18"/>
-      <c r="M6" s="18"/>
-      <c r="N6" s="18"/>
-      <c r="O6" s="18"/>
-      <c r="P6" s="19"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="24"/>
+      <c r="K6" s="24"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="24"/>
+      <c r="P6" s="25"/>
     </row>
     <row r="7" ht="56.65" customHeight="1" spans="1:16">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="18"/>
-      <c r="K7" s="18"/>
-      <c r="L7" s="18"/>
-      <c r="M7" s="18"/>
-      <c r="N7" s="18"/>
-      <c r="O7" s="18"/>
-      <c r="P7" s="19"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="24"/>
+      <c r="I7" s="24"/>
+      <c r="J7" s="24"/>
+      <c r="K7" s="24"/>
+      <c r="L7" s="24"/>
+      <c r="M7" s="24"/>
+      <c r="N7" s="24"/>
+      <c r="O7" s="24"/>
+      <c r="P7" s="25"/>
     </row>
     <row r="8" ht="56.65" customHeight="1" spans="1:16">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="18"/>
-      <c r="K8" s="18"/>
-      <c r="L8" s="18"/>
-      <c r="M8" s="18"/>
-      <c r="N8" s="18"/>
-      <c r="O8" s="18"/>
-      <c r="P8" s="19"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="24"/>
+      <c r="I8" s="24"/>
+      <c r="J8" s="24"/>
+      <c r="K8" s="24"/>
+      <c r="L8" s="24"/>
+      <c r="M8" s="24"/>
+      <c r="N8" s="24"/>
+      <c r="O8" s="24"/>
+      <c r="P8" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4263,68 +4310,68 @@
   </cols>
   <sheetData>
     <row r="1" ht="56.65" customHeight="1" spans="1:16">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18"/>
-      <c r="P1" s="19"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
+      <c r="P1" s="25"/>
     </row>
     <row r="2" ht="56.65" customHeight="1" spans="1:16">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="P2" s="21"/>
+      <c r="P2" s="27"/>
     </row>
     <row r="3" ht="56.65" customHeight="1" spans="1:16">
-      <c r="A3" s="22"/>
-      <c r="P3" s="21"/>
+      <c r="A3" s="28"/>
+      <c r="P3" s="27"/>
     </row>
     <row r="4" ht="56.65" customHeight="1" spans="1:16">
-      <c r="A4" s="22"/>
-      <c r="P4" s="21"/>
+      <c r="A4" s="28"/>
+      <c r="P4" s="27"/>
     </row>
     <row r="5" ht="56.65" customHeight="1" spans="1:16">
-      <c r="A5" s="22"/>
-      <c r="P5" s="21"/>
+      <c r="A5" s="28"/>
+      <c r="P5" s="27"/>
     </row>
     <row r="6" ht="56.65" customHeight="1" spans="1:16">
-      <c r="A6" s="22"/>
-      <c r="P6" s="21"/>
+      <c r="A6" s="28"/>
+      <c r="P6" s="27"/>
     </row>
     <row r="7" ht="56.65" customHeight="1" spans="1:16">
-      <c r="A7" s="22"/>
-      <c r="P7" s="21"/>
+      <c r="A7" s="28"/>
+      <c r="P7" s="27"/>
     </row>
     <row r="8" ht="56.65" customHeight="1" spans="1:16">
-      <c r="A8" s="23"/>
-      <c r="B8" s="24"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="24"/>
-      <c r="H8" s="24"/>
-      <c r="I8" s="24"/>
-      <c r="J8" s="24"/>
-      <c r="K8" s="24"/>
-      <c r="L8" s="24"/>
-      <c r="M8" s="24"/>
-      <c r="N8" s="24"/>
-      <c r="O8" s="24"/>
-      <c r="P8" s="25"/>
+      <c r="A8" s="29"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="30"/>
+      <c r="K8" s="30"/>
+      <c r="L8" s="30"/>
+      <c r="M8" s="30"/>
+      <c r="N8" s="30"/>
+      <c r="O8" s="30"/>
+      <c r="P8" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4964,44 +5011,44 @@
         <v>105</v>
       </c>
       <c r="B3" s="9"/>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="7" t="s">
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="7" t="s">
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="4"/>
+      <c r="L3" s="18"/>
+      <c r="M3" s="18"/>
+      <c r="N3" s="18"/>
+      <c r="O3" s="18"/>
+      <c r="P3" s="19"/>
     </row>
     <row r="4" s="16" customFormat="1" ht="56.65" customHeight="1" spans="1:16">
       <c r="A4" s="10"/>
       <c r="B4" s="12"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="21"/>
+      <c r="N4" s="21"/>
+      <c r="O4" s="21"/>
+      <c r="P4" s="22"/>
     </row>
     <row r="5" s="16" customFormat="1" ht="56.65" customHeight="1" spans="1:16">
       <c r="A5" s="6" t="s">
@@ -5093,14 +5140,16 @@
     </row>
     <row r="9" ht="56.65" customHeight="1" spans="1:16">
       <c r="A9" s="6" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="6" t="s">
+        <v>140</v>
+      </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
@@ -5111,23 +5160,27 @@
       <c r="O9" s="3"/>
       <c r="P9" s="4"/>
     </row>
-    <row r="10" spans="1:16">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
-      <c r="O10" s="7"/>
-      <c r="P10" s="7"/>
+    <row r="10" ht="49" customHeight="1" spans="1:16">
+      <c r="A10" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="4"/>
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="7"/>
@@ -5166,12 +5219,9 @@
       <c r="P12" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="18">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="G3:J3"/>
-    <mergeCell ref="K3:P3"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:P5"/>
     <mergeCell ref="A6:F6"/>
@@ -5180,8 +5230,14 @@
     <mergeCell ref="G7:P7"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="G8:P8"/>
-    <mergeCell ref="A9:P9"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="G9:P9"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="G10:P10"/>
     <mergeCell ref="A3:B4"/>
+    <mergeCell ref="C3:F4"/>
+    <mergeCell ref="G3:J4"/>
+    <mergeCell ref="K3:P4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -5201,7 +5257,7 @@
   <sheetData>
     <row r="1" ht="95" customHeight="1" spans="1:16">
       <c r="A1" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -5221,7 +5277,7 @@
     </row>
     <row r="2" ht="56.65" customHeight="1" spans="1:16">
       <c r="A2" s="5" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -5241,7 +5297,7 @@
     </row>
     <row r="3" ht="56.65" customHeight="1" spans="1:16">
       <c r="A3" s="7" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B3" s="9"/>
       <c r="C3" s="7" t="s">
@@ -5285,7 +5341,7 @@
     </row>
     <row r="5" ht="56.65" customHeight="1" spans="1:16">
       <c r="A5" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -5293,7 +5349,7 @@
       <c r="E5" s="3"/>
       <c r="F5" s="4"/>
       <c r="G5" s="6" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
@@ -5307,7 +5363,7 @@
     </row>
     <row r="6" ht="56.65" customHeight="1" spans="1:16">
       <c r="A6" s="6" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -5315,7 +5371,7 @@
       <c r="E6" s="3"/>
       <c r="F6" s="4"/>
       <c r="G6" s="6" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
@@ -5329,7 +5385,7 @@
     </row>
     <row r="7" ht="56.65" customHeight="1" spans="1:16">
       <c r="A7" s="6" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -5337,7 +5393,7 @@
       <c r="E7" s="3"/>
       <c r="F7" s="4"/>
       <c r="G7" s="6" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
@@ -5351,7 +5407,7 @@
     </row>
     <row r="8" ht="56.65" customHeight="1" spans="1:16">
       <c r="A8" s="6" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -5359,7 +5415,7 @@
       <c r="E8" s="3"/>
       <c r="F8" s="4"/>
       <c r="G8" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
@@ -5373,7 +5429,7 @@
     </row>
     <row r="9" ht="56.65" customHeight="1" spans="1:16">
       <c r="A9" s="6" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -5481,7 +5537,7 @@
   <sheetData>
     <row r="1" ht="95" customHeight="1" spans="1:16">
       <c r="A1" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -5501,7 +5557,7 @@
     </row>
     <row r="2" ht="56.65" customHeight="1" spans="1:16">
       <c r="A2" s="5" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -5565,7 +5621,7 @@
     </row>
     <row r="5" ht="56.65" customHeight="1" spans="1:16">
       <c r="A5" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -5573,7 +5629,7 @@
       <c r="E5" s="3"/>
       <c r="F5" s="4"/>
       <c r="G5" s="6" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
@@ -5587,7 +5643,7 @@
     </row>
     <row r="6" ht="56.65" customHeight="1" spans="1:16">
       <c r="A6" s="6" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -5595,7 +5651,7 @@
       <c r="E6" s="3"/>
       <c r="F6" s="4"/>
       <c r="G6" s="6" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
@@ -5609,7 +5665,7 @@
     </row>
     <row r="7" ht="56.65" customHeight="1" spans="1:16">
       <c r="A7" s="6" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -5617,7 +5673,7 @@
       <c r="E7" s="3"/>
       <c r="F7" s="4"/>
       <c r="G7" s="6" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
@@ -5631,7 +5687,7 @@
     </row>
     <row r="8" ht="56.65" customHeight="1" spans="1:16">
       <c r="A8" s="6" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -5639,7 +5695,7 @@
       <c r="E8" s="3"/>
       <c r="F8" s="4"/>
       <c r="G8" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
@@ -5653,7 +5709,7 @@
     </row>
     <row r="9" ht="56.65" customHeight="1" spans="1:16">
       <c r="A9" s="6" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -5763,7 +5819,7 @@
   <sheetData>
     <row r="1" ht="95" customHeight="1" spans="1:16">
       <c r="A1" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -5783,7 +5839,7 @@
     </row>
     <row r="2" ht="56.65" customHeight="1" spans="1:16">
       <c r="A2" s="5" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -5803,7 +5859,7 @@
     </row>
     <row r="3" ht="56.65" customHeight="1" spans="1:16">
       <c r="A3" s="6" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -5811,7 +5867,7 @@
       <c r="E3" s="3"/>
       <c r="F3" s="4"/>
       <c r="G3" s="6" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
@@ -5825,7 +5881,7 @@
     </row>
     <row r="4" ht="56.65" customHeight="1" spans="1:16">
       <c r="A4" s="6" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -5833,7 +5889,7 @@
       <c r="E4" s="3"/>
       <c r="F4" s="4"/>
       <c r="G4" s="6" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
@@ -5847,7 +5903,7 @@
     </row>
     <row r="5" ht="56.65" customHeight="1" spans="1:16">
       <c r="A5" s="6" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -5869,7 +5925,7 @@
     </row>
     <row r="6" ht="56.65" customHeight="1" spans="1:16">
       <c r="A6" s="6" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -5891,7 +5947,7 @@
     </row>
     <row r="7" ht="56.65" customHeight="1" spans="1:16">
       <c r="A7" s="6" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -5899,7 +5955,7 @@
       <c r="E7" s="3"/>
       <c r="F7" s="4"/>
       <c r="G7" s="6" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
@@ -5913,7 +5969,7 @@
     </row>
     <row r="8" ht="56.65" customHeight="1" spans="1:16">
       <c r="A8" s="6" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -5933,7 +5989,7 @@
     </row>
     <row r="9" ht="56.65" customHeight="1" spans="1:16">
       <c r="A9" s="6" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
